--- a/每日预测/Aii竞彩推荐_2026-05-12.xlsx
+++ b/每日预测/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 16:42</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:15</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP6.85/3.95/1.37 让球-1</t>
+          <t>SP7.10/3.95/1.36 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP3.04/3.30/2.01 让球+1</t>
+          <t>SP2.92/3.45/2.01 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.15/3.34/1.95 让球-1</t>
+          <t>SP3.29/3.20/1.95 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.50/3.20/2.40 让球-1</t>
+          <t>SP2.56/3.10/2.40 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP4.35/3.55/1.62 让球-1</t>
+          <t>SP4.48/3.55/1.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 16:42</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:15</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6.85</v>
+        <v>7.1</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>3.95</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>2.01</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>1.95</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>2.4</v>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>3.55</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.64</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分0-1|半全场负负|大小球小2.5(42%)|让球+1=输盘/让胜|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=34%P平=28%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=29%P客=34%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       <c r="C79" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)</t>
+·圣旺红星:客胜(1.60)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62=3.16</t>
+          <t>1.95×1.60=3.12</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       <c r="C80" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)</t>
         </is>
       </c>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62×1.50=4.74</t>
+          <t>1.95×1.60×1.50=4.68</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       <c r="C81" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)
 ·奥萨苏纳:客胜(1.47)</t>
         </is>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62×1.50×1.47=6.97</t>
+          <t>1.95×1.60×1.50×1.47=6.88</t>
         </is>
       </c>
     </row>
@@ -3123,8 +3123,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：6.85 / 3.95 / 1.37
-竞彩SP: 2.60/2.70/2.67
+欧赔(spf)：7.1 / 3.95 / 1.36
+竞彩SP: 2.65/2.65/2.67
 差值分析：P主=31% P平=29% P客=40%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3143,11 +3143,11 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：3.04 / 3.3 / 2.01
-竞彩SP: 8.10/4.45/1.28
+欧赔(spf)：2.92 / 3.45 / 2.01
+竞彩SP: 7.65/4.60/1.28
 差值分析：P主=35% P平=30% P客=35%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3163,9 +3163,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：3.15 / 3.34 / 1.95
+欧赔(spf)：3.29 / 3.2 / 1.95
 竞彩SP: 1.67/3.60/3.95
-差值分析：P主=34% P平=28% P客=38%
+差值分析：P主=34% P平=28% P客=37%
 推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
         </is>
@@ -3203,9 +3203,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：2.5 / 3.2 / 2.4
+欧赔(spf)：2.56 / 3.1 / 2.4
 竞彩SP: 1.44/4.10/5.25
-差值分析：P主=38% P平=29% P客=34%
+差值分析：P主=38% P平=29% P客=33%
 推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3223,8 +3223,8 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：4.35 / 3.55 / 1.62
-竞彩SP: 2.00/3.02/3.35
+欧赔(spf)：4.48 / 3.55 / 1.6
+竞彩SP: 2.03/2.96/3.35
 差值分析：P主=32% P平=29% P客=39%
 推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3264,7 +3264,7 @@
           <t xml:space="preserve">时间：03:30
 联赛：西甲
 欧赔(spf)：5.2 / 3.9 / 1.47
-竞彩SP: 2.31/3.25/2.57
+竞彩SP: 2.31/3.15/2.64
 差值分析：P主=28% P平=26% P客=46%
 推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 穿盘=让胜 </t>
@@ -3376,7 +3376,7 @@
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)</t>
+·圣旺红星:客胜(1.60)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>3.16倍</t>
+          <t>3.12倍</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)</t>
         </is>
       </c>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.74倍</t>
+          <t>4.68倍</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       <c r="C6" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)
 ·奥萨苏纳:客胜(1.47)</t>
         </is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>6.97倍</t>
+          <t>6.88倍</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>79元</t>
+          <t>78元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>79.00倍</t>
+          <t>78.00倍</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>592.00</t>
+          <t>585.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>592元</t>
+          <t>585元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>592.00倍</t>
+          <t>585.00倍</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.74倍</t>
+          <t>4.68倍</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>6.97倍</t>
+          <t>6.88倍</t>
         </is>
       </c>
     </row>

--- a/每日预测/Aii竞彩推荐_2026-05-12.xlsx
+++ b/每日预测/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:15</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:28</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP7.10/3.95/1.36 让球-1</t>
+          <t>SP8.50/4.25/1.29 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.92/3.45/2.01 让球+1</t>
+          <t>SP2.82/3.45/2.06 让球+1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:15</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:28</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.42</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>3.45</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.30</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -3123,9 +3123,9 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：7.1 / 3.95 / 1.36
-竞彩SP: 2.65/2.65/2.67
-差值分析：P主=31% P平=29% P客=40%
+欧赔(spf)：8.5 / 4.25 / 1.29
+竞彩SP: 2.95/2.65/2.42
+差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
         </is>
@@ -3143,9 +3143,9 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：2.92 / 3.45 / 2.01
-竞彩SP: 7.65/4.60/1.28
-差值分析：P主=35% P平=30% P客=35%
+欧赔(spf)：2.82 / 3.45 / 2.06
+竞彩SP: 7.00/4.60/1.30
+差值分析：P主=36% P平=30% P客=34%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>

--- a/每日预测/Aii竞彩推荐_2026-05-12.xlsx
+++ b/每日预测/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:28</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:58</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP8.50/4.25/1.29 让球-1</t>
+          <t>SP6.25/3.85/1.41 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.82/3.45/2.06 让球+1</t>
+          <t>SP7.00/4.60/1.30 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.29/3.20/1.95 让球-1</t>
+          <t>SP1.67/3.60/3.95 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP4.05/4.00/1.58 让球-1</t>
+          <t>SP2.06/3.45/2.82 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.56/3.10/2.40 让球-1</t>
+          <t>SP1.44/4.10/5.25 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP4.48/3.55/1.60 让球-1</t>
+          <t>SP2.03/2.96/3.35 让球-1</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP4.70/4.00/1.50 让球-1</t>
+          <t>SP2.20/3.15/2.80 让球-1</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP5.20/3.90/1.47 让球-1</t>
+          <t>SP2.38/3.15/2.55 让球-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:28</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:58</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.82</v>
+        <v>7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3.29</v>
+        <v>1.67</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.95</v>
+        <v>3.95</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>4.05</v>
+        <v>2.06</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1.58</v>
+        <v>2.82</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>4.48</v>
+        <v>2.03</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.6</v>
+        <v>3.35</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=42%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=32%P平=29%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1852,17 +1852,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=27%P客=38%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
+          <t>贝叶斯P主=44%P平=29%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=28%P平=26%P客=46%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2845,13 +2845,13 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60=3.12</t>
+          <t>1.67×1.44=2.40</t>
         </is>
       </c>
     </row>
@@ -2881,14 +2881,14 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60×1.50=4.68</t>
+          <t>1.67×1.44×2.03=4.88</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.47)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)
+·奥萨苏纳:主胜(2.38)</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60×1.50×1.47=6.88</t>
+          <t>1.67×1.44×2.03×2.38=11.62</t>
         </is>
       </c>
     </row>
@@ -3123,31 +3123,31 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：8.5 / 4.25 / 1.29
-竞彩SP: 2.95/2.65/2.42
+欧赔(spf)：6.25 / 3.85 / 1.41
+竞彩SP: 3.15/2.65/2.30
+差值分析：P主=31% P平=29% P客=40%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二002 光州FC vs 首尔FC [韩职] 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：18:30
+联赛：韩职
+欧赔(spf)：7.0 / 4.6 / 1.3
+竞彩SP: 2.82/3.45/2.06
 差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>⚽ 周二002 光州FC vs 首尔FC [韩职] 18:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：18:30
-联赛：韩职
-欧赔(spf)：2.82 / 3.45 / 2.06
-竞彩SP: 7.00/4.60/1.30
-差值分析：P主=36% P平=30% P客=34%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让+1 走水=让平 </t>
+让球:让+1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：3.29 / 3.2 / 1.95
-竞彩SP: 1.67/3.60/3.95
-差值分析：P主=34% P平=28% P客=37%
-推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：1.67 / 3.6 / 3.95
+竞彩SP: 3.35/3.10/1.97
+差值分析：P主=44% P平=27% P客=29%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3183,11 +3183,11 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-欧赔(spf)：4.05 / 4.0 / 1.58
-竞彩SP: 2.06/3.45/2.82
-差值分析：P主=33% P平=28% P客=39%
-推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：2.06 / 3.45 / 2.82
+竞彩SP: 4.05/4.00/1.58
+差值分析：P主=42% P平=28% P客=29%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3203,10 +3203,10 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：2.56 / 3.1 / 2.4
-竞彩SP: 1.44/4.10/5.25
-差值分析：P主=38% P平=29% P客=33%
-推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+欧赔(spf)：1.44 / 4.1 / 5.25
+竞彩SP: 2.56/3.10/2.40
+差值分析：P主=49% P平=26% P客=25%
+推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3223,11 +3223,11 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：4.48 / 3.55 / 1.6
-竞彩SP: 2.03/2.96/3.35
-差值分析：P主=32% P平=29% P客=39%
-推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：2.03 / 2.96 / 3.35
+竞彩SP: 4.48/3.55/1.60
+差值分析：P主=42% P平=30% P客=28%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3243,11 +3243,11 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-欧赔(spf)：4.7 / 4.0 / 1.5
-竞彩SP: 2.20/3.15/2.80
-差值分析：P主=34% P平=27% P客=38%
-推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让-1 穿盘=让胜 </t>
+欧赔(spf)：2.2 / 3.15 / 2.8
+竞彩SP: 4.70/4.00/1.50
+差值分析：P主=44% P平=29% P客=27%
+推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3263,11 +3263,11 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-欧赔(spf)：5.2 / 3.9 / 1.47
-竞彩SP: 2.31/3.15/2.64
-差值分析：P主=28% P平=26% P客=46%
-推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让-1 穿盘=让胜 </t>
+欧赔(spf)：2.38 / 3.15 / 2.55
+竞彩SP: 5.55/4.00/1.43
+差值分析：P主=40% P平=27% P客=33%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3370,13 +3370,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>6元</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>3.12倍</t>
+          <t>2.40倍</t>
         </is>
       </c>
     </row>
@@ -3411,14 +3411,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>9元</t>
+          <t>10元</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.68倍</t>
+          <t>4.88倍</t>
         </is>
       </c>
     </row>
@@ -3453,15 +3453,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.47)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)
+·奥萨苏纳:主胜(2.38)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>14元</t>
+          <t>23元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>6.88倍</t>
+          <t>11.62倍</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>78元</t>
+          <t>60元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>78.00倍</t>
+          <t>60.00倍</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>585.00</t>
+          <t>610.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>585元</t>
+          <t>610元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>585.00倍</t>
+          <t>610.00倍</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.68倍</t>
+          <t>4.88倍</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>7元</t>
+          <t>12元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>6.88倍</t>
+          <t>11.62倍</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>6元</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>6.25倍</t>
+          <t>4.84倍</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>16元</t>
+          <t>11元</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>15.62倍</t>
+          <t>10.65倍</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>39.06</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>39元</t>
+          <t>23元</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>39.06倍</t>
+          <t>23.43倍</t>
         </is>
       </c>
     </row>
